--- a/data/trans_dic/P19C02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C02-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,29; 30,73</t>
+          <t>21,03; 30,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,0; 27,74</t>
+          <t>19,53; 28,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,6; 38,95</t>
+          <t>28,66; 39,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36,7; 54,51</t>
+          <t>35,81; 53,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,5; 33,27</t>
+          <t>24,57; 33,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,43; 31,53</t>
+          <t>21,64; 31,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,15; 38,91</t>
+          <t>28,96; 38,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,68; 45,68</t>
+          <t>31,58; 46,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,07; 30,62</t>
+          <t>24,31; 30,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,87; 28,39</t>
+          <t>21,71; 28,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,32; 37,58</t>
+          <t>29,85; 36,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,41; 48,16</t>
+          <t>36,03; 48,02</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,1; 43,25</t>
+          <t>35,15; 43,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,28; 40,07</t>
+          <t>31,94; 40,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,36; 45,39</t>
+          <t>36,06; 44,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,63; 61,28</t>
+          <t>48,88; 62,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,43; 42,55</t>
+          <t>34,1; 42,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,75; 39,95</t>
+          <t>32,23; 41,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,15; 42,4</t>
+          <t>33,88; 42,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,84; 55,61</t>
+          <t>29,06; 55,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,59; 41,5</t>
+          <t>35,54; 41,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,41; 39,24</t>
+          <t>33,21; 38,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,29; 42,35</t>
+          <t>36,37; 42,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,65; 56,31</t>
+          <t>39,99; 56,34</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,87; 40,81</t>
+          <t>31,91; 40,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,66; 42,9</t>
+          <t>34,43; 42,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,09; 46,53</t>
+          <t>38,42; 46,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,81; 60,67</t>
+          <t>51,65; 60,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,39; 38,24</t>
+          <t>30,05; 38,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,18; 43,09</t>
+          <t>35,47; 43,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,18; 48,32</t>
+          <t>40,8; 48,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,37; 60,47</t>
+          <t>53,16; 60,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,91; 37,9</t>
+          <t>32,04; 37,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,4; 42,04</t>
+          <t>36,43; 42,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40,46; 46,44</t>
+          <t>40,51; 46,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53,56; 59,44</t>
+          <t>53,52; 59,41</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,36; 35,55</t>
+          <t>25,88; 35,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,67; 38,54</t>
+          <t>29,44; 38,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,81; 41,76</t>
+          <t>33,12; 42,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,61; 51,48</t>
+          <t>15,81; 51,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,55; 36,51</t>
+          <t>28,06; 37,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,34; 43,14</t>
+          <t>34,69; 43,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,5; 48,37</t>
+          <t>39,81; 48,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,46; 55,81</t>
+          <t>44,28; 55,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,74; 34,8</t>
+          <t>28,56; 35,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,58; 39,61</t>
+          <t>33,43; 39,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,79; 43,9</t>
+          <t>37,53; 44,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,07; 52,08</t>
+          <t>24,48; 52,28</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,16; 24,51</t>
+          <t>14,78; 24,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,1; 28,33</t>
+          <t>19,08; 28,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,43; 33,41</t>
+          <t>23,83; 33,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41,7; 49,62</t>
+          <t>41,92; 49,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,46; 30,07</t>
+          <t>20,32; 29,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,65; 33,74</t>
+          <t>24,02; 34,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,18; 40,23</t>
+          <t>29,56; 39,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,84; 54,28</t>
+          <t>47,99; 54,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,03; 25,66</t>
+          <t>19,14; 26,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,06; 29,73</t>
+          <t>23,2; 29,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28,0; 35,1</t>
+          <t>27,89; 35,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>46,09; 51,03</t>
+          <t>45,84; 50,99</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,53; 14,47</t>
+          <t>6,48; 14,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,17; 18,36</t>
+          <t>9,57; 18,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,01; 27,23</t>
+          <t>17,15; 27,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35,0; 43,46</t>
+          <t>35,17; 43,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,55; 22,75</t>
+          <t>13,66; 22,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,07; 23,09</t>
+          <t>13,63; 22,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,3; 35,89</t>
+          <t>24,64; 35,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42,44; 85,8</t>
+          <t>42,01; 84,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,87; 17,3</t>
+          <t>10,89; 17,18</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,93; 19,41</t>
+          <t>13,08; 19,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,23; 30,02</t>
+          <t>22,5; 30,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40,54; 76,09</t>
+          <t>40,69; 75,8</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,07; 9,8</t>
+          <t>2,08; 10,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,65; 21,61</t>
+          <t>9,54; 20,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,95; 26,14</t>
+          <t>13,6; 25,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,33; 29,98</t>
+          <t>21,74; 29,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 9,53</t>
+          <t>2,58; 8,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,32; 16,13</t>
+          <t>7,91; 15,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,52; 26,45</t>
+          <t>13,79; 26,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,82; 32,11</t>
+          <t>25,61; 31,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,8</t>
+          <t>2,87; 8,19</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,84; 16,61</t>
+          <t>10,0; 16,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,47; 23,87</t>
+          <t>15,36; 24,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,88; 30,14</t>
+          <t>25,1; 30,2</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,9; 30,63</t>
+          <t>26,83; 30,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,84; 31,4</t>
+          <t>27,93; 31,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,01; 36,66</t>
+          <t>32,92; 36,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,83; 47,58</t>
+          <t>34,02; 47,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,54; 30,81</t>
+          <t>27,3; 30,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,73; 33,05</t>
+          <t>29,37; 32,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,21; 39,06</t>
+          <t>35,29; 38,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>46,02; 59,53</t>
+          <t>45,82; 58,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27,57; 30,16</t>
+          <t>27,63; 30,1</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29,42; 31,81</t>
+          <t>29,25; 31,71</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34,7; 37,32</t>
+          <t>34,8; 37,42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,91; 50,97</t>
+          <t>42,19; 50,88</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>76512; 110456</t>
+          <t>75581; 108180</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72028; 105197</t>
+          <t>74052; 106347</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100924; 137421</t>
+          <t>101133; 137942</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>140712; 209030</t>
+          <t>137293; 205678</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>92194; 125175</t>
+          <t>92451; 125810</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83227; 116976</t>
+          <t>80267; 115035</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>102583; 136936</t>
+          <t>101916; 135806</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>96157; 138662</t>
+          <t>95850; 141132</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>177096; 225221</t>
+          <t>178851; 226021</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>164054; 212984</t>
+          <t>162828; 210132</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>213673; 264872</t>
+          <t>210343; 259729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>250116; 330831</t>
+          <t>247514; 329890</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>202110; 249038</t>
+          <t>202410; 250510</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>192819; 239322</t>
+          <t>190779; 239884</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>179262; 223793</t>
+          <t>177807; 221126</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>195673; 246561</t>
+          <t>196655; 250587</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>188260; 232609</t>
+          <t>186438; 232733</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>177777; 223680</t>
+          <t>180443; 229690</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>169617; 210616</t>
+          <t>168291; 210690</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>154082; 277863</t>
+          <t>145206; 279558</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>399485; 465827</t>
+          <t>398954; 464453</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>386543; 454014</t>
+          <t>384224; 451155</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>359243; 419134</t>
+          <t>360008; 418347</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>357674; 507973</t>
+          <t>360700; 508194</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>160286; 205248</t>
+          <t>160469; 202339</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>203352; 251657</t>
+          <t>201958; 250305</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>212508; 259549</t>
+          <t>214357; 259796</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>271483; 317915</t>
+          <t>270683; 317776</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>183444; 230795</t>
+          <t>181398; 230269</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>232335; 284568</t>
+          <t>234210; 285625</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>230271; 276936</t>
+          <t>233792; 279656</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>283846; 321613</t>
+          <t>282735; 321021</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>353118; 419355</t>
+          <t>354567; 417328</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>453861; 524297</t>
+          <t>454245; 524479</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>457602; 525192</t>
+          <t>458197; 524301</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>565502; 627649</t>
+          <t>565166; 627324</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>106673; 143905</t>
+          <t>104730; 144801</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>161059; 209215</t>
+          <t>159813; 209366</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>168118; 213959</t>
+          <t>169679; 215639</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>134581; 443711</t>
+          <t>136262; 442577</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>120708; 159972</t>
+          <t>122963; 162552</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>193444; 243048</t>
+          <t>195443; 245140</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>215254; 263574</t>
+          <t>216894; 264767</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>297472; 390973</t>
+          <t>310236; 390859</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>242228; 293334</t>
+          <t>240765; 295094</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>371469; 438196</t>
+          <t>369746; 437329</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>399551; 464163</t>
+          <t>396772; 466412</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>407307; 813829</t>
+          <t>382575; 816955</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>41286; 66759</t>
+          <t>40240; 66577</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>68629; 101784</t>
+          <t>68539; 101536</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86908; 123963</t>
+          <t>88399; 123949</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>227909; 271211</t>
+          <t>229124; 272588</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>65295; 95961</t>
+          <t>64845; 95461</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92414; 131809</t>
+          <t>93831; 132909</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>119457; 159277</t>
+          <t>117015; 157249</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>255708; 290145</t>
+          <t>256545; 291222</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>112548; 151791</t>
+          <t>113182; 154070</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>172918; 222930</t>
+          <t>173969; 224804</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>214751; 269191</t>
+          <t>213857; 270187</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>498272; 551692</t>
+          <t>495619; 551205</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13890; 30797</t>
+          <t>13793; 31307</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23974; 48009</t>
+          <t>25020; 47758</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36836; 62661</t>
+          <t>39476; 64202</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>125764; 156187</t>
+          <t>126368; 156333</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33336; 55976</t>
+          <t>33601; 55616</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42303; 69409</t>
+          <t>40982; 68979</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67300; 99398</t>
+          <t>68232; 99404</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>254605; 514749</t>
+          <t>252019; 506044</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>49847; 79375</t>
+          <t>49968; 78806</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72651; 109123</t>
+          <t>73500; 109735</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>112738; 152246</t>
+          <t>114083; 154011</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>388894; 729934</t>
+          <t>390357; 727165</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2618; 12428</t>
+          <t>2634; 13489</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17854; 39970</t>
+          <t>17646; 38245</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20509; 38436</t>
+          <t>20001; 37664</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58930; 82807</t>
+          <t>60051; 82434</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4655; 19841</t>
+          <t>5368; 18371</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25157; 48786</t>
+          <t>23923; 47493</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33090; 60271</t>
+          <t>31429; 59689</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>105510; 131243</t>
+          <t>104674; 130562</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9729; 26132</t>
+          <t>9625; 27445</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47938; 80954</t>
+          <t>48728; 79292</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58007; 89500</t>
+          <t>57597; 90335</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>170393; 206437</t>
+          <t>171936; 206843</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>660275; 751819</t>
+          <t>658676; 746373</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>810594; 914182</t>
+          <t>813097; 915239</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>879600; 976764</t>
+          <t>877134; 974335</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1134610; 1595896</t>
+          <t>1140942; 1588859</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>754103; 843476</t>
+          <t>747514; 844575</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>935900; 1040413</t>
+          <t>924557; 1035890</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1009448; 1119982</t>
+          <t>1011762; 1112294</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1646831; 2130632</t>
+          <t>1639898; 2089353</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1431757; 1566168</t>
+          <t>1434830; 1562899</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1782601; 1927511</t>
+          <t>1772288; 1921758</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1919510; 2064428</t>
+          <t>1924967; 2070108</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2905594; 3533389</t>
+          <t>2925284; 3527322</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C02-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,03; 30,1</t>
+          <t>21,48; 30,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,53; 28,05</t>
+          <t>18,91; 27,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,66; 39,09</t>
+          <t>28,2; 38,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,81; 53,64</t>
+          <t>36,69; 53,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,57; 33,44</t>
+          <t>24,54; 33,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,64; 31,01</t>
+          <t>21,54; 31,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,96; 38,59</t>
+          <t>28,78; 38,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,58; 46,5</t>
+          <t>35,7; 49,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,31; 30,72</t>
+          <t>24,19; 30,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,71; 28,01</t>
+          <t>21,7; 28,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,85; 36,85</t>
+          <t>29,88; 37,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,03; 48,02</t>
+          <t>37,84; 48,71</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>54,93%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,15; 43,51</t>
+          <t>34,9; 43,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,94; 40,16</t>
+          <t>31,97; 40,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,06; 44,85</t>
+          <t>36,25; 44,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,88; 62,28</t>
+          <t>49,51; 62,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,1; 42,57</t>
+          <t>34,0; 42,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,23; 41,03</t>
+          <t>32,1; 40,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,88; 42,42</t>
+          <t>34,12; 42,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,06; 55,95</t>
+          <t>48,67; 58,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,54; 41,38</t>
+          <t>35,86; 41,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,21; 38,99</t>
+          <t>33,02; 39,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,37; 42,27</t>
+          <t>36,33; 42,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,99; 56,34</t>
+          <t>51,26; 58,46</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>55,45%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,91; 40,23</t>
+          <t>31,94; 40,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,43; 42,67</t>
+          <t>34,72; 43,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,42; 46,57</t>
+          <t>38,16; 46,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,65; 60,64</t>
+          <t>50,24; 58,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,05; 38,15</t>
+          <t>30,12; 37,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,47; 43,25</t>
+          <t>35,78; 43,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,8; 48,8</t>
+          <t>40,75; 48,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,16; 60,36</t>
+          <t>52,87; 59,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,04; 37,72</t>
+          <t>32,04; 38,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,43; 42,06</t>
+          <t>36,44; 41,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40,51; 46,36</t>
+          <t>40,57; 46,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53,52; 59,41</t>
+          <t>52,35; 58,27</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>52,25%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,88; 35,78</t>
+          <t>26,37; 35,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,44; 38,57</t>
+          <t>29,74; 38,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,12; 42,09</t>
+          <t>33,37; 42,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,81; 51,35</t>
+          <t>45,9; 53,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,06; 37,1</t>
+          <t>27,87; 36,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,69; 43,51</t>
+          <t>34,32; 43,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,81; 48,59</t>
+          <t>39,44; 48,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44,28; 55,79</t>
+          <t>51,01; 57,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,56; 35,01</t>
+          <t>28,24; 34,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,43; 39,53</t>
+          <t>33,45; 39,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,53; 44,12</t>
+          <t>37,77; 43,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,48; 52,28</t>
+          <t>49,61; 54,45</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,81%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,78; 24,45</t>
+          <t>14,85; 24,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,08; 28,26</t>
+          <t>19,41; 28,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,83; 33,41</t>
+          <t>23,64; 33,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41,92; 49,87</t>
+          <t>42,26; 50,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,32; 29,92</t>
+          <t>20,91; 30,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,02; 34,02</t>
+          <t>24,33; 34,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,56; 39,72</t>
+          <t>29,66; 39,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,99; 54,48</t>
+          <t>47,96; 54,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,14; 26,05</t>
+          <t>18,88; 25,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,2; 29,98</t>
+          <t>23,01; 29,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,89; 35,23</t>
+          <t>27,94; 35,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>45,84; 50,99</t>
+          <t>46,42; 51,27</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,48; 14,71</t>
+          <t>6,23; 14,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,57; 18,26</t>
+          <t>9,31; 18,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,15; 27,9</t>
+          <t>16,84; 27,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35,17; 43,5</t>
+          <t>36,33; 44,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,66; 22,61</t>
+          <t>13,28; 22,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,63; 22,95</t>
+          <t>14,02; 23,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,64; 35,89</t>
+          <t>23,69; 35,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42,01; 84,35</t>
+          <t>40,35; 47,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,89; 17,18</t>
+          <t>11,24; 17,47</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,08; 19,52</t>
+          <t>13,06; 19,24</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,5; 30,37</t>
+          <t>22,39; 30,11</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40,69; 75,8</t>
+          <t>39,53; 44,95</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 10,64</t>
+          <t>1,84; 10,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,54; 20,68</t>
+          <t>9,9; 20,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,6; 25,61</t>
+          <t>13,96; 26,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,74; 29,84</t>
+          <t>21,96; 30,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 8,82</t>
+          <t>2,27; 9,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,91; 15,7</t>
+          <t>8,54; 16,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,79; 26,19</t>
+          <t>14,25; 25,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,61; 31,95</t>
+          <t>26,25; 33,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,19</t>
+          <t>2,77; 8,06</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,0; 16,27</t>
+          <t>9,85; 15,97</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,36; 24,09</t>
+          <t>15,52; 23,67</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,1; 30,2</t>
+          <t>25,61; 30,6</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,92%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,83; 30,41</t>
+          <t>26,88; 30,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,93; 31,43</t>
+          <t>27,83; 31,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,92; 36,57</t>
+          <t>32,97; 36,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34,02; 47,37</t>
+          <t>45,16; 49,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,3; 30,85</t>
+          <t>27,48; 30,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,37; 32,9</t>
+          <t>29,4; 32,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,29; 38,79</t>
+          <t>35,27; 39,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>45,82; 58,38</t>
+          <t>47,25; 50,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27,63; 30,1</t>
+          <t>27,61; 30,05</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29,25; 31,71</t>
+          <t>29,34; 31,73</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34,8; 37,42</t>
+          <t>34,79; 37,42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>42,19; 50,88</t>
+          <t>46,59; 49,1</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>171977</t>
+          <t>170139</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>116932</t>
+          <t>144522</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>288909</t>
+          <t>314661</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>75581; 108180</t>
+          <t>77193; 111100</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74052; 106347</t>
+          <t>71710; 104956</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101133; 137942</t>
+          <t>99495; 136219</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>137293; 205678</t>
+          <t>139002; 200897</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>92451; 125810</t>
+          <t>92337; 127734</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80267; 115035</t>
+          <t>79929; 115002</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>101916; 135806</t>
+          <t>101287; 135152</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>95850; 141132</t>
+          <t>122534; 169568</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>178851; 226021</t>
+          <t>177988; 225393</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>162828; 210132</t>
+          <t>162795; 210485</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>210343; 259729</t>
+          <t>210565; 261239</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>247514; 329890</t>
+          <t>273234; 351755</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>222667</t>
+          <t>249887</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>232506</t>
+          <t>260120</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>455173</t>
+          <t>510007</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>202410; 250510</t>
+          <t>200974; 248843</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>190779; 239884</t>
+          <t>190965; 240548</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>177807; 221126</t>
+          <t>178728; 220972</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>196655; 250587</t>
+          <t>220778; 276443</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>186438; 232733</t>
+          <t>185872; 232227</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>180443; 229690</t>
+          <t>179693; 226757</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>168291; 210690</t>
+          <t>169469; 210468</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>145206; 279558</t>
+          <t>234863; 281070</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>398954; 464453</t>
+          <t>402568; 466663</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>384224; 451155</t>
+          <t>382089; 451990</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>360008; 418347</t>
+          <t>359603; 419102</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>360700; 508194</t>
+          <t>475927; 542809</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>294726</t>
+          <t>329066</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>302627</t>
+          <t>341049</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>597354</t>
+          <t>670114</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>160469; 202339</t>
+          <t>160654; 203206</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>201958; 250305</t>
+          <t>203688; 254552</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>214357; 259796</t>
+          <t>212889; 261117</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>270683; 317776</t>
+          <t>302004; 353186</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>181398; 230269</t>
+          <t>181801; 227025</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>234210; 285625</t>
+          <t>236281; 287111</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>233792; 279656</t>
+          <t>233518; 278436</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>282735; 321021</t>
+          <t>321043; 361712</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>354567; 417328</t>
+          <t>354501; 421633</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>454245; 524479</t>
+          <t>454433; 521139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>458197; 524301</t>
+          <t>458812; 527547</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>565166; 627324</t>
+          <t>632658; 704141</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309573</t>
+          <t>338762</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>362261</t>
+          <t>392262</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>671833</t>
+          <t>731024</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>104730; 144801</t>
+          <t>106722; 145358</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>159813; 209366</t>
+          <t>161458; 208131</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>169679; 215639</t>
+          <t>170970; 215341</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136262; 442577</t>
+          <t>310887; 363838</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>122963; 162552</t>
+          <t>122133; 160564</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>195443; 245140</t>
+          <t>193322; 242858</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>216894; 264767</t>
+          <t>214887; 262467</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>310236; 390859</t>
+          <t>368169; 411470</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>240765; 295094</t>
+          <t>238003; 294812</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>369746; 437329</t>
+          <t>370042; 438952</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>396772; 466412</t>
+          <t>399339; 462580</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>382575; 816955</t>
+          <t>694152; 761758</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>249555</t>
+          <t>273933</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>274325</t>
+          <t>306476</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>523881</t>
+          <t>580409</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>40240; 66577</t>
+          <t>40439; 66385</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>68539; 101536</t>
+          <t>69746; 102283</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88399; 123949</t>
+          <t>87721; 125342</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>229124; 272588</t>
+          <t>250781; 298354</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>64845; 95461</t>
+          <t>66719; 96542</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93831; 132909</t>
+          <t>95067; 132841</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>117015; 157249</t>
+          <t>117432; 156304</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>256545; 291222</t>
+          <t>285777; 323342</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>113182; 154070</t>
+          <t>111635; 152050</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>173969; 224804</t>
+          <t>172602; 222463</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>213857; 270187</t>
+          <t>214266; 270069</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>495619; 551205</t>
+          <t>552003; 609698</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>141190</t>
+          <t>161130</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>376215</t>
+          <t>187807</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>517405</t>
+          <t>348937</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13793; 31307</t>
+          <t>13264; 30879</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25020; 47758</t>
+          <t>24345; 48416</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39476; 64202</t>
+          <t>38744; 63383</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>126368; 156333</t>
+          <t>144517; 178081</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33601; 55616</t>
+          <t>32666; 56089</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40982; 68979</t>
+          <t>42132; 69138</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68232; 99404</t>
+          <t>65596; 97282</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>252019; 506044</t>
+          <t>173060; 202652</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>49968; 78806</t>
+          <t>51553; 80165</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>73500; 109735</t>
+          <t>73436; 108136</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>114083; 154011</t>
+          <t>113555; 152694</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>390357; 727165</t>
+          <t>326819; 371553</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>70926</t>
+          <t>79349</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>117344</t>
+          <t>131329</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>188270</t>
+          <t>210678</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2634; 13489</t>
+          <t>2333; 12732</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17646; 38245</t>
+          <t>18314; 37980</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20001; 37664</t>
+          <t>20535; 38385</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>60051; 82434</t>
+          <t>66623; 91806</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5368; 18371</t>
+          <t>4721; 19575</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23923; 47493</t>
+          <t>25811; 48532</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31429; 59689</t>
+          <t>32476; 57969</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>104674; 130562</t>
+          <t>117013; 147281</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9625; 27445</t>
+          <t>9269; 27002</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>48728; 79292</t>
+          <t>48018; 77844</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>57597; 90335</t>
+          <t>58172; 88766</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>171936; 206843</t>
+          <t>191824; 229244</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1460614</t>
+          <t>1602266</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1782210</t>
+          <t>1763564</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3242824</t>
+          <t>3365829</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>658676; 746373</t>
+          <t>659841; 748681</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>813097; 915239</t>
+          <t>810338; 915626</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>877134; 974335</t>
+          <t>878313; 979996</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1140942; 1588859</t>
+          <t>1534252; 1669016</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>747514; 844575</t>
+          <t>752463; 845461</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>924557; 1035890</t>
+          <t>925666; 1036465</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1011762; 1112294</t>
+          <t>1011202; 1118218</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1639898; 2089353</t>
+          <t>1713086; 1816654</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1434830; 1562899</t>
+          <t>1433902; 1560556</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1772288; 1921758</t>
+          <t>1778019; 1922867</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1924967; 2070108</t>
+          <t>1924204; 2069709</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2925284; 3527322</t>
+          <t>3272423; 3448444</t>
         </is>
       </c>
     </row>
